--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-17.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-17.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_2B59D187542AB9251F383E11593278F35B29D2E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66F13FA8-BF66-4983-AAEA-51902C8F5EBF}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_2B59D187542AB9251F383E11593278F35B29D2E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C50C8A54-2A17-420D-9E26-326D4E3F0D86}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,9 +103,6 @@
     <t>LAY</t>
   </si>
   <si>
-    <t>vs</t>
-  </si>
-  <si>
     <t>PENDENTE</t>
   </si>
   <si>
@@ -248,6 +245,9 @@
   </si>
   <si>
     <t>5x0</t>
+  </si>
+  <si>
+    <t>1x1</t>
   </si>
 </sst>
 </file>
@@ -323,6 +323,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -710,13 +714,13 @@
         <v>100</v>
       </c>
       <c r="N2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" t="s">
         <v>28</v>
-      </c>
-      <c r="R2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -727,22 +731,22 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>31</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>32</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>33</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>34</v>
-      </c>
-      <c r="H3" t="s">
-        <v>35</v>
       </c>
       <c r="I3" t="s">
         <v>26</v>
@@ -760,13 +764,13 @@
         <v>100</v>
       </c>
       <c r="N3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O3" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" t="s">
         <v>28</v>
-      </c>
-      <c r="R3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -774,25 +778,25 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
         <v>36</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>37</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>38</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>39</v>
       </c>
-      <c r="F4" t="s">
-        <v>40</v>
-      </c>
       <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s">
         <v>34</v>
-      </c>
-      <c r="H4" t="s">
-        <v>35</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -810,13 +814,13 @@
         <v>100</v>
       </c>
       <c r="N4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O4" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" t="s">
         <v>28</v>
-      </c>
-      <c r="R4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -824,25 +828,25 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
         <v>41</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>42</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>43</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>44</v>
       </c>
-      <c r="F5" t="s">
-        <v>45</v>
-      </c>
       <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
         <v>34</v>
-      </c>
-      <c r="H5" t="s">
-        <v>35</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
@@ -860,13 +864,13 @@
         <v>100</v>
       </c>
       <c r="N5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O5" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" t="s">
         <v>28</v>
-      </c>
-      <c r="R5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -874,25 +878,25 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
         <v>46</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>47</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>48</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>49</v>
       </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
       <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s">
         <v>34</v>
-      </c>
-      <c r="H6" t="s">
-        <v>35</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
@@ -910,13 +914,13 @@
         <v>100</v>
       </c>
       <c r="N6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O6" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" t="s">
         <v>28</v>
-      </c>
-      <c r="R6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -924,25 +928,25 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
         <v>51</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>52</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>53</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>54</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>55</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>56</v>
-      </c>
-      <c r="H7" t="s">
-        <v>57</v>
       </c>
       <c r="I7" t="s">
         <v>26</v>
@@ -960,13 +964,13 @@
         <v>100</v>
       </c>
       <c r="N7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O7" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" t="s">
         <v>28</v>
-      </c>
-      <c r="R7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -974,25 +978,25 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
         <v>58</v>
       </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>59</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>60</v>
       </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
       <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" t="s">
         <v>34</v>
-      </c>
-      <c r="H8" t="s">
-        <v>35</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
@@ -1010,13 +1014,13 @@
         <v>100</v>
       </c>
       <c r="N8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O8" t="s">
+        <v>27</v>
+      </c>
+      <c r="R8" t="s">
         <v>28</v>
-      </c>
-      <c r="R8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -1024,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
         <v>62</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>63</v>
       </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
       <c r="G9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" t="s">
         <v>34</v>
-      </c>
-      <c r="H9" t="s">
-        <v>35</v>
       </c>
       <c r="I9" t="s">
         <v>26</v>
@@ -1060,13 +1064,13 @@
         <v>100</v>
       </c>
       <c r="N9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R9" t="s">
         <v>28</v>
-      </c>
-      <c r="R9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -1074,25 +1078,25 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
         <v>65</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>66</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>67</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>68</v>
       </c>
-      <c r="F10" t="s">
-        <v>69</v>
-      </c>
       <c r="G10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" t="s">
         <v>34</v>
-      </c>
-      <c r="H10" t="s">
-        <v>35</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
@@ -1110,13 +1114,13 @@
         <v>100</v>
       </c>
       <c r="N10" t="s">
+        <v>75</v>
+      </c>
+      <c r="O10" t="s">
         <v>27</v>
       </c>
-      <c r="O10" t="s">
+      <c r="R10" t="s">
         <v>28</v>
-      </c>
-      <c r="R10" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-17.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-17.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -543,37 +553,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SERBIA 2</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FK Loznica x FK Javor Ivanjica</t>
+          <t>ZED FC x Olympic El Qanal</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FK Loznica</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FK Javor Ivanjica</t>
+          <t>Olympic El Qanal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -582,20 +592,20 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3.03</v>
+        <v>6.9</v>
       </c>
       <c r="M2" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2x2</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -610,9 +620,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>6.66</v>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -627,32 +645,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ESTONIA 1</t>
+          <t>SERBIA 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FCI Tallinn x Tammeka Tartu</t>
+          <t>FK Loznica x FK Javor Ivanjica</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>FK Loznica</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>FK Javor Ivanjica</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -661,20 +679,20 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="K3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>15.62</v>
+        <v>3.03</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>6x0</t>
+          <t>2x2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -692,6 +710,8 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -701,27 +721,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EUROPA LEAGUE</t>
+          <t>ESTONIA 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OFI x Hoffenheim</t>
+          <t>FCI Tallinn x Tammeka Tartu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -740,20 +760,20 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="K4" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="L4" t="n">
-        <v>19.23</v>
+        <v>15.62</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>6x0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -771,6 +791,8 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -780,27 +802,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EGYPT 1</t>
+          <t>EUROPA LEAGUE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ENPPI x Pyramids</t>
+          <t>OFI x Hoffenheim</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -819,20 +841,20 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="K5" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="L5" t="n">
-        <v>23.26</v>
+        <v>19.23</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -850,6 +872,8 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -859,27 +883,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SOUTH AFRICA 1</t>
+          <t>EGYPT 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Orlando Pirates (SA) x Durban City</t>
+          <t>ENPPI x Pyramids</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orlando Pirates (SA)</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -901,7 +925,7 @@
         <v>5.3</v>
       </c>
       <c r="K6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="L6" t="n">
         <v>23.26</v>
@@ -911,7 +935,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -929,6 +953,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -938,37 +964,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SERBIA 1</t>
+          <t>SOUTH AFRICA 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zeleznicar Pancevo x Crvena Zvezda</t>
+          <t>Orlando Pirates (SA) x Durban City</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zeleznicar Pancevo</t>
+          <t>Orlando Pirates (SA)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Crvena Zvezda</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -977,20 +1003,20 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="K7" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="L7" t="n">
-        <v>14.71</v>
+        <v>23.26</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1008,6 +1034,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1017,37 +1045,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EUROPA LEAGUE</t>
+          <t>SOUTH AFRICA 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Crystal Palace x Lech Poznan</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Crystal Palace</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Lech Poznan</t>
-        </is>
-      </c>
+          <t>Orlando Pirates x Durban City</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1056,37 +1076,45 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="L8" t="n">
-        <v>20.41</v>
+        <v>7.14</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4x0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1096,37 +1124,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EUROPA LEAGUE</t>
+          <t>SERBIA 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Juventus x NEC Nijmegen</t>
+          <t>Zeleznicar Pancevo x Crvena Zvezda</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Zeleznicar Pancevo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>Crvena Zvezda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1135,20 +1163,20 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="K9" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="L9" t="n">
-        <v>12.2</v>
+        <v>14.71</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>5x0</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1166,6 +1194,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1175,27 +1205,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>COPA LIBERTADORES</t>
+          <t>EUROPA LEAGUE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Flamengo x Independiente (Ecu)</t>
+          <t>Crystal Palace x Lech Poznan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Independiente (Ecu)</t>
+          <t>Lech Poznan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1214,20 +1244,20 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="L10" t="n">
-        <v>20</v>
+        <v>20.41</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1x1</t>
+          <t>4x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1245,6 +1275,8 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1254,29 +1286,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SOUTH AFRICA 1</t>
+          <t>EUROPA LEAGUE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Orlando Pirates x Durban City</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>Juventus x NEC Nijmegen</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1285,43 +1325,209 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="L11" t="n">
-        <v>7.14</v>
+        <v>12.2</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>5x0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>COLOMBIA 1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bucaramanga x Ind. Medellin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ind. Medellin</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="M12" t="n">
+        <v>200</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2x2</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="P12" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="W12" t="n">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>COPA LIBERTADORES</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Flamengo x Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Independiente (Ecu)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L13" t="n">
+        <v>20</v>
+      </c>
+      <c r="M13" t="n">
+        <v>100</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-17.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-17.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,19 +605,19 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S2" t="n">
